--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -1062,7 +1062,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -110,397 +110,398 @@
     <t>수집품 - 도감 및 컬렉션 아이템</t>
   </si>
   <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>장비 - 무기</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>장비 - 방어구</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>장비 - 장신구</t>
+  </si>
+  <si>
+    <t>Relic</t>
+  </si>
+  <si>
+    <t>장비 - 유물</t>
+  </si>
+  <si>
+    <t>Crafting</t>
+  </si>
+  <si>
+    <t>재료 - 제작 재료</t>
+  </si>
+  <si>
+    <t>Enhance</t>
+  </si>
+  <si>
+    <t>재료 - 장비 강화 재료</t>
+  </si>
+  <si>
+    <t>Usable</t>
+  </si>
+  <si>
+    <t>소모품 - 물약</t>
+  </si>
+  <si>
+    <t>Box</t>
+  </si>
+  <si>
+    <t>소모품 - 아이템 상자</t>
+  </si>
+  <si>
+    <t>SkillBook</t>
+  </si>
+  <si>
+    <t>소모품 - 스킬포인트 획득</t>
+  </si>
+  <si>
+    <t>Costume</t>
+  </si>
+  <si>
+    <t>수집품 - 코스튬</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>일반</t>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>고급</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>희귀</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>영웅</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>전설</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>신화</t>
+  </si>
+  <si>
+    <t>DropTier</t>
+  </si>
+  <si>
+    <t>Tier_1</t>
+  </si>
+  <si>
+    <t>Tier_2</t>
+  </si>
+  <si>
+    <t>Tier_3</t>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>!ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>MainCategory</t>
+  </si>
+  <si>
+    <t>SubCategory</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>MaxStack</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
+    <t>!string</t>
+  </si>
+  <si>
+    <t>!ItemMainCategory</t>
+  </si>
+  <si>
+    <t>!ItemSubCategory</t>
+  </si>
+  <si>
+    <t>!ItemGradeType</t>
+  </si>
+  <si>
+    <t>!DropTier</t>
+  </si>
+  <si>
+    <t>쌍검</t>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_2</t>
+  </si>
+  <si>
+    <t>룬소드</t>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_1</t>
+  </si>
+  <si>
+    <t>석궁</t>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_3</t>
+  </si>
+  <si>
+    <t>쌍권총</t>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_4</t>
+  </si>
+  <si>
+    <t>강철 투구</t>
+  </si>
+  <si>
+    <t>근접 투구 방어구</t>
+  </si>
+  <si>
+    <t>ItemIcon_Armor_1</t>
+  </si>
+  <si>
+    <t>가죽 후드</t>
+  </si>
+  <si>
+    <t>원거리 투구 방어구</t>
+  </si>
+  <si>
+    <t>ItemIcon_Armor_2</t>
+  </si>
+  <si>
+    <t>강철 갑옷</t>
+  </si>
+  <si>
+    <t>근접 갑옷방어구</t>
+  </si>
+  <si>
+    <t>가죽 로브</t>
+  </si>
+  <si>
+    <t>원거리 갑옷 방어구</t>
+  </si>
+  <si>
+    <t>강철 장갑</t>
+  </si>
+  <si>
+    <t>근접 장갑 방어구</t>
+  </si>
+  <si>
+    <t>가죽 장갑</t>
+  </si>
+  <si>
+    <t>원거리 장갑 방어구</t>
+  </si>
+  <si>
+    <t>강철 신발</t>
+  </si>
+  <si>
+    <t>근접 신발 방어구</t>
+  </si>
+  <si>
+    <t>ItemIcon_Boots_1</t>
+  </si>
+  <si>
+    <t>가죽 신발</t>
+  </si>
+  <si>
+    <t>원거리 신발 방어구</t>
+  </si>
+  <si>
+    <t>ItemIcon_Boots_2</t>
+  </si>
+  <si>
+    <t>근접 반지</t>
+  </si>
+  <si>
+    <t>근접 반지 장신구</t>
+  </si>
+  <si>
+    <t>ItemIcon_Ring_1</t>
+  </si>
+  <si>
+    <t>원거리 반지</t>
+  </si>
+  <si>
+    <t>원거리 반지 장신구</t>
+  </si>
+  <si>
+    <t>근접 목걸이</t>
+  </si>
+  <si>
+    <t>근접 목걸이 장신구</t>
+  </si>
+  <si>
+    <t>ItemIcon_Amulet_1</t>
+  </si>
+  <si>
+    <t>원거리 목걸이</t>
+  </si>
+  <si>
+    <t>원거리 목걸이 장신구</t>
+  </si>
+  <si>
+    <t>근접 유물</t>
+  </si>
+  <si>
+    <t>ItemIcon_Relic_1</t>
+  </si>
+  <si>
+    <t>원거리 유물</t>
+  </si>
+  <si>
+    <t>무기 강화 주문서</t>
+  </si>
+  <si>
+    <t>무기를 강화하는데 사용한다.</t>
+  </si>
+  <si>
+    <t>ItemIcon_WeaponScroll</t>
+  </si>
+  <si>
+    <t>방어구 강화 주문서</t>
+  </si>
+  <si>
+    <t>방어구를 강화하는데 사용한다.</t>
+  </si>
+  <si>
+    <t>ItemIcon_ArmorScroll</t>
+  </si>
+  <si>
+    <t>장신구 강화 주문서</t>
+  </si>
+  <si>
+    <t>장신구를 강화하는데 사용한다.</t>
+  </si>
+  <si>
+    <t>ItemIcon_AccessoryScroll</t>
+  </si>
+  <si>
+    <t>지식의 서</t>
+  </si>
+  <si>
+    <t>스킬 포인트 획득</t>
+  </si>
+  <si>
+    <t>ItemIcon_SkillBook</t>
+  </si>
+  <si>
+    <t>하급 회복 물약</t>
+  </si>
+  <si>
+    <t>체력을 소량 회복한다</t>
+  </si>
+  <si>
+    <t>ItemIcon_Potion_HpSmall</t>
+  </si>
+  <si>
+    <t>상급 회복 물약</t>
+  </si>
+  <si>
+    <t>체력을 대량 회복한다</t>
+  </si>
+  <si>
+    <t>ItemIcon_Potion_HpLarge</t>
+  </si>
+  <si>
+    <t>공격력 비약</t>
+  </si>
+  <si>
+    <t>일정 시간 공격력이 증가한다</t>
+  </si>
+  <si>
+    <t>ItemIcon_Scroll_Atk</t>
+  </si>
+  <si>
+    <t>일반 상자</t>
+  </si>
+  <si>
+    <t>개봉하면 보상을 획득한다</t>
+  </si>
+  <si>
+    <t>ItemIcon_Box_Normal</t>
+  </si>
+  <si>
+    <t>10연 상자</t>
+  </si>
+  <si>
+    <t>개봉하면 보상을 10회 획득한다</t>
+  </si>
+  <si>
+    <t>ItemIcon_Box_Multi</t>
+  </si>
+  <si>
+    <t>청동 열쇠</t>
+  </si>
+  <si>
+    <t>일반 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>ItemIcon_Key_Bronze</t>
+  </si>
+  <si>
+    <t>은 열쇠</t>
+  </si>
+  <si>
+    <t>고급 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>ItemIcon_Key_Silver</t>
+  </si>
+  <si>
+    <t>금 열쇠</t>
+  </si>
+  <si>
+    <t>최고급 보물 상자를 여는데 사용한다.</t>
+  </si>
+  <si>
+    <t>ItemIcon_Key_Gold</t>
+  </si>
+  <si>
+    <t>ItemGradeType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>ItemSubCategory</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>장비 - 무기</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>장비 - 방어구</t>
-  </si>
-  <si>
-    <t>Accessory</t>
-  </si>
-  <si>
-    <t>장비 - 장신구</t>
-  </si>
-  <si>
-    <t>Relic</t>
-  </si>
-  <si>
-    <t>장비 - 유물</t>
-  </si>
-  <si>
-    <t>Crafting</t>
-  </si>
-  <si>
-    <t>재료 - 제작 재료</t>
-  </si>
-  <si>
-    <t>Enhance</t>
-  </si>
-  <si>
-    <t>재료 - 장비 강화 재료</t>
-  </si>
-  <si>
-    <t>Usable</t>
-  </si>
-  <si>
-    <t>소모품 - 물약</t>
-  </si>
-  <si>
-    <t>Box</t>
-  </si>
-  <si>
-    <t>소모품 - 아이템 상자</t>
-  </si>
-  <si>
-    <t>SkillBook</t>
-  </si>
-  <si>
-    <t>소모품 - 스킬포인트 획득</t>
-  </si>
-  <si>
-    <t>Costume</t>
-  </si>
-  <si>
-    <t>수집품 - 코스튬</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>일반</t>
-  </si>
-  <si>
-    <t>Magic</t>
-  </si>
-  <si>
-    <t>고급</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>희귀</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>영웅</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>전설</t>
-  </si>
-  <si>
-    <t>Mythic</t>
-  </si>
-  <si>
-    <t>신화</t>
-  </si>
-  <si>
-    <t>DropTier</t>
-  </si>
-  <si>
-    <t>Tier_1</t>
-  </si>
-  <si>
-    <t>Tier_2</t>
-  </si>
-  <si>
-    <t>Tier_3</t>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>!ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>MainCategory</t>
-  </si>
-  <si>
-    <t>SubCategory</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>MaxStack</t>
-  </si>
-  <si>
-    <t>!int</t>
-  </si>
-  <si>
-    <t>!string</t>
-  </si>
-  <si>
-    <t>!ItemMainCategory</t>
-  </si>
-  <si>
-    <t>!ItemSubCategory</t>
-  </si>
-  <si>
-    <t>!ItemGradeType</t>
-  </si>
-  <si>
-    <t>!DropTier</t>
-  </si>
-  <si>
-    <t>쌍검</t>
-  </si>
-  <si>
-    <t>ItemIcon_Weapon_2</t>
-  </si>
-  <si>
-    <t>룬소드</t>
-  </si>
-  <si>
-    <t>ItemIcon_Weapon_1</t>
-  </si>
-  <si>
-    <t>석궁</t>
-  </si>
-  <si>
-    <t>ItemIcon_Weapon_3</t>
-  </si>
-  <si>
-    <t>쌍권총</t>
-  </si>
-  <si>
-    <t>ItemIcon_Weapon_4</t>
-  </si>
-  <si>
-    <t>강철 투구</t>
-  </si>
-  <si>
-    <t>근접 투구 방어구</t>
-  </si>
-  <si>
-    <t>ItemIcon_Armor_1</t>
-  </si>
-  <si>
-    <t>가죽 후드</t>
-  </si>
-  <si>
-    <t>원거리 투구 방어구</t>
-  </si>
-  <si>
-    <t>ItemIcon_Armor_2</t>
-  </si>
-  <si>
-    <t>강철 갑옷</t>
-  </si>
-  <si>
-    <t>근접 갑옷방어구</t>
-  </si>
-  <si>
-    <t>가죽 로브</t>
-  </si>
-  <si>
-    <t>원거리 갑옷 방어구</t>
-  </si>
-  <si>
-    <t>강철 장갑</t>
-  </si>
-  <si>
-    <t>근접 장갑 방어구</t>
-  </si>
-  <si>
-    <t>가죽 장갑</t>
-  </si>
-  <si>
-    <t>원거리 장갑 방어구</t>
-  </si>
-  <si>
-    <t>강철 신발</t>
-  </si>
-  <si>
-    <t>근접 신발 방어구</t>
-  </si>
-  <si>
-    <t>ItemIcon_Boots_1</t>
-  </si>
-  <si>
-    <t>가죽 신발</t>
-  </si>
-  <si>
-    <t>원거리 신발 방어구</t>
-  </si>
-  <si>
-    <t>ItemIcon_Boots_2</t>
-  </si>
-  <si>
-    <t>근접 반지</t>
-  </si>
-  <si>
-    <t>근접 반지 장신구</t>
-  </si>
-  <si>
-    <t>ItemIcon_Ring_1</t>
-  </si>
-  <si>
-    <t>원거리 반지</t>
-  </si>
-  <si>
-    <t>원거리 반지 장신구</t>
-  </si>
-  <si>
-    <t>근접 목걸이</t>
-  </si>
-  <si>
-    <t>근접 목걸이 장신구</t>
-  </si>
-  <si>
-    <t>ItemIcon_Amulet_1</t>
-  </si>
-  <si>
-    <t>원거리 목걸이</t>
-  </si>
-  <si>
-    <t>원거리 목걸이 장신구</t>
-  </si>
-  <si>
-    <t>근접 유물</t>
-  </si>
-  <si>
-    <t>ItemIcon_Relic_1</t>
-  </si>
-  <si>
-    <t>원거리 유물</t>
-  </si>
-  <si>
-    <t>무기 강화 주문서</t>
-  </si>
-  <si>
-    <t>무기를 강화하는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_WeaponScroll</t>
-  </si>
-  <si>
-    <t>방어구 강화 주문서</t>
-  </si>
-  <si>
-    <t>방어구를 강화하는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_ArmorScroll</t>
-  </si>
-  <si>
-    <t>장신구 강화 주문서</t>
-  </si>
-  <si>
-    <t>장신구를 강화하는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_AccessoryScroll</t>
-  </si>
-  <si>
-    <t>지식의 서</t>
-  </si>
-  <si>
-    <t>스킬 포인트 획득</t>
-  </si>
-  <si>
-    <t>ItemIcon_SkillBook</t>
-  </si>
-  <si>
-    <t>하급 회복 물약</t>
-  </si>
-  <si>
-    <t>체력을 소량 회복한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Potion_HpSmall</t>
-  </si>
-  <si>
-    <t>상급 회복 물약</t>
-  </si>
-  <si>
-    <t>체력을 대량 회복한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Potion_HpLarge</t>
-  </si>
-  <si>
-    <t>공격력 비약</t>
-  </si>
-  <si>
-    <t>일정 시간 공격력이 증가한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Scroll_Atk</t>
-  </si>
-  <si>
-    <t>일반 상자</t>
-  </si>
-  <si>
-    <t>개봉하면 보상을 획득한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Box_Normal</t>
-  </si>
-  <si>
-    <t>10연 상자</t>
-  </si>
-  <si>
-    <t>개봉하면 보상을 10회 획득한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Box_Multi</t>
-  </si>
-  <si>
-    <t>청동 열쇠</t>
-  </si>
-  <si>
-    <t>일반 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_Key_Bronze</t>
-  </si>
-  <si>
-    <t>은 열쇠</t>
-  </si>
-  <si>
-    <t>고급 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_Key_Silver</t>
-  </si>
-  <si>
-    <t>금 열쇠</t>
-  </si>
-  <si>
-    <t>최고급 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_Key_Gold</t>
-  </si>
-  <si>
-    <t>ItemGradeType</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1062,7 +1063,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1130,88 +1131,88 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>11</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>15</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>19</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>21</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>25</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>27</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>29</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1219,56 +1220,56 @@
         <v>0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="15"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>31</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>33</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>41</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1276,23 +1277,23 @@
         <v>0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="15"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B28" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1322,40 +1323,40 @@
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="I2" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
         <v>55</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" t="s">
-        <v>56</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -1365,31 +1366,31 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="I3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="20" t="s">
-        <v>62</v>
-      </c>
       <c r="J3" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
@@ -1402,25 +1403,25 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>64</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J4" s="11">
         <v>1</v>
@@ -1431,25 +1432,25 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J5" s="11">
         <v>1</v>
@@ -1461,25 +1462,25 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>68</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" s="11">
         <v>1</v>
@@ -1491,25 +1492,25 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>70</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J7" s="11">
         <v>1</v>
@@ -1520,25 +1521,25 @@
         <v>1010202001</v>
       </c>
       <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>73</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J8" s="11">
         <v>1</v>
@@ -1549,25 +1550,25 @@
         <v>1010202002</v>
       </c>
       <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J9" s="11">
         <v>1</v>
@@ -1578,25 +1579,25 @@
         <v>1010203001</v>
       </c>
       <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="E10" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="11">
         <v>1</v>
@@ -1607,25 +1608,25 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>80</v>
-      </c>
       <c r="E11" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J11" s="11">
         <v>1</v>
@@ -1636,25 +1637,25 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>82</v>
-      </c>
       <c r="E12" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J12" s="11">
         <v>1</v>
@@ -1665,25 +1666,25 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>84</v>
-      </c>
       <c r="E13" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J13" s="11">
         <v>1</v>
@@ -1694,25 +1695,25 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J14" s="11">
         <v>1</v>
@@ -1723,25 +1724,25 @@
         <v>1010205002</v>
       </c>
       <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J15" s="11">
         <v>1</v>
@@ -1752,25 +1753,25 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>93</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J16" s="11">
         <v>1</v>
@@ -1781,25 +1782,25 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="E17" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J17" s="11">
         <v>1</v>
@@ -1810,25 +1811,25 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J18" s="11">
         <v>1</v>
@@ -1839,25 +1840,25 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>100</v>
-      </c>
       <c r="E19" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J19" s="11">
         <v>1</v>
@@ -1868,25 +1869,25 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J20" s="11">
         <v>1</v>
@@ -1897,25 +1898,25 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J21" s="11">
         <v>1</v>
@@ -1926,22 +1927,22 @@
         <v>1020200001</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22" s="21"/>
     </row>
@@ -1950,22 +1951,22 @@
         <v>1020200002</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>109</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="21"/>
     </row>
@@ -1974,22 +1975,22 @@
         <v>1020200003</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>112</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" s="21"/>
     </row>
@@ -1998,25 +1999,25 @@
         <v>1030300001</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
@@ -2024,22 +2025,22 @@
         <v>1030100001</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
@@ -2047,22 +2048,22 @@
         <v>1030100002</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
@@ -2070,22 +2071,22 @@
         <v>1030100003</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -2093,22 +2094,22 @@
         <v>1030200001</v>
       </c>
       <c r="C29" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
@@ -2116,22 +2117,22 @@
         <v>1030200002</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>130</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
@@ -2139,22 +2140,22 @@
         <v>1020100001</v>
       </c>
       <c r="C31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" t="s">
         <v>131</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>132</v>
-      </c>
-      <c r="E31" t="s">
-        <v>133</v>
       </c>
       <c r="F31" t="s">
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I31" s="21"/>
     </row>
@@ -2163,22 +2164,22 @@
         <v>1020100002</v>
       </c>
       <c r="C32" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" t="s">
         <v>134</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>135</v>
-      </c>
-      <c r="E32" t="s">
-        <v>136</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I32" s="21"/>
     </row>
@@ -2187,22 +2188,22 @@
         <v>1020100003</v>
       </c>
       <c r="C33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" t="s">
         <v>137</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>138</v>
-      </c>
-      <c r="E33" t="s">
-        <v>139</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="123">
   <si>
     <t>!Enum</t>
   </si>
@@ -389,33 +389,6 @@
     <t>원거리 유물</t>
   </si>
   <si>
-    <t>무기 강화 주문서</t>
-  </si>
-  <si>
-    <t>무기를 강화하는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_WeaponScroll</t>
-  </si>
-  <si>
-    <t>방어구 강화 주문서</t>
-  </si>
-  <si>
-    <t>방어구를 강화하는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_ArmorScroll</t>
-  </si>
-  <si>
-    <t>장신구 강화 주문서</t>
-  </si>
-  <si>
-    <t>장신구를 강화하는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_AccessoryScroll</t>
-  </si>
-  <si>
     <t>지식의 서</t>
   </si>
   <si>
@@ -468,33 +441,6 @@
   </si>
   <si>
     <t>ItemIcon_Box_Multi</t>
-  </si>
-  <si>
-    <t>청동 열쇠</t>
-  </si>
-  <si>
-    <t>일반 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_Key_Bronze</t>
-  </si>
-  <si>
-    <t>은 열쇠</t>
-  </si>
-  <si>
-    <t>고급 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_Key_Silver</t>
-  </si>
-  <si>
-    <t>금 열쇠</t>
-  </si>
-  <si>
-    <t>최고급 보물 상자를 여는데 사용한다.</t>
-  </si>
-  <si>
-    <t>ItemIcon_Key_Gold</t>
   </si>
   <si>
     <t>ItemGradeType</t>
@@ -1063,7 +1009,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1131,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C7" s="15"/>
     </row>
@@ -1220,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C19" s="15"/>
     </row>
@@ -1305,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9" customWidth="1"/>
@@ -1923,8 +1869,8 @@
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="11">
-        <v>1020200001</v>
+      <c r="B22">
+        <v>1030300001</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>103</v>
@@ -1936,19 +1882,21 @@
         <v>105</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
-        <v>1020200002</v>
+        <v>1030100001</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>106</v>
@@ -1960,19 +1908,18 @@
         <v>108</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I23" s="21"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
-        <v>1020200003</v>
+        <v>1030100002</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>109</v>
@@ -1984,19 +1931,18 @@
         <v>111</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="21"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25">
-        <v>1030300001</v>
+      <c r="B25" s="11">
+        <v>1030100003</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>112</v>
@@ -2011,18 +1957,15 @@
         <v>6</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
-        <v>1030100001</v>
+        <v>1030200001</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>115</v>
@@ -2037,7 +1980,7 @@
         <v>6</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>30</v>
@@ -2045,7 +1988,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
-        <v>1030100002</v>
+        <v>1030200002</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>118</v>
@@ -2060,150 +2003,10 @@
         <v>6</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="11">
-        <v>1030100003</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="11">
-        <v>1030200001</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="11">
-        <v>1030200002</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31">
-        <v>1020100001</v>
-      </c>
-      <c r="C31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" t="s">
-        <v>132</v>
-      </c>
-      <c r="F31" t="s">
-        <v>4</v>
-      </c>
-      <c r="G31" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="21"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32">
-        <v>1020100002</v>
-      </c>
-      <c r="C32" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" t="s">
-        <v>135</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="21"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33">
-        <v>1020100003</v>
-      </c>
-      <c r="C33" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" t="s">
-        <v>138</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="136">
   <si>
     <t>!Enum</t>
   </si>
@@ -149,12 +149,6 @@
     <t>소모품 - 물약</t>
   </si>
   <si>
-    <t>Box</t>
-  </si>
-  <si>
-    <t>소모품 - 아이템 상자</t>
-  </si>
-  <si>
     <t>SkillBook</t>
   </si>
   <si>
@@ -396,51 +390,6 @@
   </si>
   <si>
     <t>ItemIcon_SkillBook</t>
-  </si>
-  <si>
-    <t>하급 회복 물약</t>
-  </si>
-  <si>
-    <t>체력을 소량 회복한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Potion_HpSmall</t>
-  </si>
-  <si>
-    <t>상급 회복 물약</t>
-  </si>
-  <si>
-    <t>체력을 대량 회복한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Potion_HpLarge</t>
-  </si>
-  <si>
-    <t>공격력 비약</t>
-  </si>
-  <si>
-    <t>일정 시간 공격력이 증가한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Scroll_Atk</t>
-  </si>
-  <si>
-    <t>일반 상자</t>
-  </si>
-  <si>
-    <t>개봉하면 보상을 획득한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Box_Normal</t>
-  </si>
-  <si>
-    <t>10연 상자</t>
-  </si>
-  <si>
-    <t>개봉하면 보상을 10회 획득한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Box_Multi</t>
   </si>
   <si>
     <t>일반 보물상자 열쇠</t>
@@ -1111,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="9" bestFit="1" customWidth="1"/>
@@ -1130,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C1" s="15"/>
     </row>
@@ -1171,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C7" s="15"/>
     </row>
@@ -1249,28 +1198,28 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="C19" s="15"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="15"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
@@ -1312,36 +1261,28 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B26" s="11" t="s">
+    <row r="27" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C27" s="15"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="21" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="C28" s="15"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="21" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9" customWidth="1"/>
@@ -1371,40 +1312,40 @@
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="F2" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="H2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="I2" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
         <v>53</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" t="s">
-        <v>55</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -1414,31 +1355,31 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="G3" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="H3" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="I3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>61</v>
-      </c>
       <c r="J3" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
@@ -1451,13 +1392,13 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>1</v>
@@ -1466,10 +1407,10 @@
         <v>9</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J4" s="11">
         <v>1</v>
@@ -1480,13 +1421,13 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>1</v>
@@ -1495,10 +1436,10 @@
         <v>9</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J5" s="11">
         <v>1</v>
@@ -1510,13 +1451,13 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>1</v>
@@ -1525,10 +1466,10 @@
         <v>9</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J6" s="11">
         <v>1</v>
@@ -1540,13 +1481,13 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>1</v>
@@ -1555,10 +1496,10 @@
         <v>9</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J7" s="11">
         <v>1</v>
@@ -1569,13 +1510,13 @@
         <v>1010202001</v>
       </c>
       <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>1</v>
@@ -1584,10 +1525,10 @@
         <v>11</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J8" s="11">
         <v>1</v>
@@ -1598,13 +1539,13 @@
         <v>1010202002</v>
       </c>
       <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>1</v>
@@ -1613,10 +1554,10 @@
         <v>11</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J9" s="11">
         <v>1</v>
@@ -1627,13 +1568,13 @@
         <v>1010203001</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>1</v>
@@ -1642,10 +1583,10 @@
         <v>11</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J10" s="11">
         <v>1</v>
@@ -1656,13 +1597,13 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>1</v>
@@ -1671,10 +1612,10 @@
         <v>11</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J11" s="11">
         <v>1</v>
@@ -1685,13 +1626,13 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>1</v>
@@ -1700,10 +1641,10 @@
         <v>11</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J12" s="11">
         <v>1</v>
@@ -1714,13 +1655,13 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>1</v>
@@ -1729,10 +1670,10 @@
         <v>11</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J13" s="11">
         <v>1</v>
@@ -1743,13 +1684,13 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>1</v>
@@ -1758,10 +1699,10 @@
         <v>11</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J14" s="11">
         <v>1</v>
@@ -1772,13 +1713,13 @@
         <v>1010205002</v>
       </c>
       <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>89</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>1</v>
@@ -1787,10 +1728,10 @@
         <v>11</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J15" s="11">
         <v>1</v>
@@ -1801,13 +1742,13 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>92</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>1</v>
@@ -1816,10 +1757,10 @@
         <v>13</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J16" s="11">
         <v>1</v>
@@ -1830,13 +1771,13 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>1</v>
@@ -1845,10 +1786,10 @@
         <v>13</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J17" s="11">
         <v>1</v>
@@ -1859,13 +1800,13 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>1</v>
@@ -1874,10 +1815,10 @@
         <v>13</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J18" s="11">
         <v>1</v>
@@ -1888,13 +1829,13 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>1</v>
@@ -1903,10 +1844,10 @@
         <v>13</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J19" s="11">
         <v>1</v>
@@ -1917,13 +1858,13 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>1</v>
@@ -1932,10 +1873,10 @@
         <v>15</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J20" s="11">
         <v>1</v>
@@ -1946,13 +1887,13 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>1</v>
@@ -1961,10 +1902,10 @@
         <v>15</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J21" s="11">
         <v>1</v>
@@ -1975,91 +1916,91 @@
         <v>1030300001</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>105</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
-        <v>1030100001</v>
+        <v>1020100001</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
-        <v>1030100002</v>
+        <v>1020100002</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
-        <v>1030100003</v>
+        <v>1020100003</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
@@ -2067,134 +2008,149 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
-        <v>1030200001</v>
+        <v>1040100001</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="J26" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
-        <v>1030200002</v>
+        <v>1040100002</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="J27" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
-        <v>1020100001</v>
+        <v>1040100003</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>30</v>
+        <v>38</v>
+      </c>
+      <c r="J28" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
-        <v>1020100002</v>
+        <v>1040200001</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="J29" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
-        <v>1020100003</v>
+        <v>1040200002</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>34</v>
+        <v>28</v>
+      </c>
+      <c r="J30" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
-        <v>1040100001</v>
+        <v>1040200003</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>131</v>
+        <v>118</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>124</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>27</v>
+        <v>120</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="J31" s="11">
         <v>1</v>
@@ -2202,25 +2158,25 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
-        <v>1040100002</v>
+        <v>1040200004</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J32" s="11">
         <v>1</v>
@@ -2228,25 +2184,25 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
-        <v>1040100003</v>
+        <v>1040200005</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J33" s="11">
         <v>1</v>
@@ -2254,157 +2210,27 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
-        <v>1040200001</v>
+        <v>1040200006</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J34" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B35" s="11">
-        <v>1040200002</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B36" s="11">
-        <v>1040200003</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" s="11">
-        <v>1040200004</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J37" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B38" s="11">
-        <v>1040200005</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J38" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B39" s="11">
-        <v>1040200006</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J39" s="11">
         <v>1</v>
       </c>
     </row>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="139">
   <si>
     <t>!Enum</t>
   </si>
@@ -260,25 +260,13 @@
     <t>!DropTier</t>
   </si>
   <si>
-    <t>쌍검</t>
-  </si>
-  <si>
     <t>ItemIcon_Weapon_2</t>
   </si>
   <si>
-    <t>룬소드</t>
-  </si>
-  <si>
     <t>ItemIcon_Weapon_1</t>
   </si>
   <si>
-    <t>석궁</t>
-  </si>
-  <si>
     <t>ItemIcon_Weapon_3</t>
-  </si>
-  <si>
-    <t>쌍권총</t>
   </si>
   <si>
     <t>ItemIcon_Weapon_4</t>
@@ -491,6 +479,34 @@
   </si>
   <si>
     <t>WeaponCostume_01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>도</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>권총</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>권총</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1052,7 +1068,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1079,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C1" s="15"/>
     </row>
@@ -1120,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C7" s="15"/>
     </row>
@@ -1198,10 +1214,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1392,13 +1408,13 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>1</v>
@@ -1421,13 +1437,13 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>1</v>
@@ -1451,13 +1467,13 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>1</v>
@@ -1481,13 +1497,13 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>1</v>
@@ -1510,13 +1526,13 @@
         <v>1010202001</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>1</v>
@@ -1539,13 +1555,13 @@
         <v>1010202002</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>1</v>
@@ -1568,13 +1584,13 @@
         <v>1010203001</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>1</v>
@@ -1597,13 +1613,13 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>1</v>
@@ -1626,13 +1642,13 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>1</v>
@@ -1655,13 +1671,13 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>1</v>
@@ -1684,13 +1700,13 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>1</v>
@@ -1713,13 +1729,13 @@
         <v>1010205002</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>1</v>
@@ -1742,13 +1758,13 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>1</v>
@@ -1771,13 +1787,13 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>1</v>
@@ -1800,13 +1816,13 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>1</v>
@@ -1829,13 +1845,13 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>1</v>
@@ -1858,13 +1874,13 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>1</v>
@@ -1887,13 +1903,13 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>1</v>
@@ -1916,13 +1932,13 @@
         <v>1030300001</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>5</v>
@@ -1942,13 +1958,13 @@
         <v>1020100001</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>3</v>
@@ -1965,13 +1981,13 @@
         <v>1020100002</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>3</v>
@@ -1988,13 +2004,13 @@
         <v>1020100003</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>3</v>
@@ -2011,10 +2027,10 @@
         <v>1040100001</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>7</v>
@@ -2031,13 +2047,13 @@
         <v>1040100002</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>7</v>
@@ -2057,13 +2073,13 @@
         <v>1040100003</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>7</v>
@@ -2083,19 +2099,19 @@
         <v>1040200001</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>28</v>
@@ -2109,19 +2125,19 @@
         <v>1040200002</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>28</v>
@@ -2135,19 +2151,19 @@
         <v>1040200003</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>28</v>
@@ -2161,19 +2177,19 @@
         <v>1040200004</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>28</v>
@@ -2187,19 +2203,19 @@
         <v>1040200005</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>28</v>
@@ -2213,19 +2229,19 @@
         <v>1040200006</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>28</v>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -490,23 +490,23 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>도</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>권총</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>권총</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>소총</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>소총</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리검</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리검</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>태도</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1068,7 +1068,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1437,10 +1437,10 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>61</v>
@@ -1467,10 +1467,10 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>62</v>
@@ -1497,10 +1497,10 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>63</v>
